--- a/doc/计划.xlsx
+++ b/doc/计划.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\code\Money\stocking\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\code\Ey\stocking\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6BB80-C4FC-4F1E-9A28-ADAF0091B1B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EA2221-8D76-4D91-B468-F1F56E7B1E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总体计划" sheetId="1" r:id="rId1"/>
@@ -939,9 +939,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -951,6 +948,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1275,7 +1275,7 @@
       <c r="B5" s="15"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="28" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -1283,23 +1283,23 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="28" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -1307,25 +1307,25 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="21" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="28" t="s">
         <v>41</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -1333,11 +1333,11 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="28" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="20" t="s">
@@ -1345,11 +1345,11 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
+      <c r="A17" s="28"/>
       <c r="B17" s="20"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="28" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="20" t="s">
@@ -1357,25 +1357,25 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
+      <c r="A20" s="28"/>
       <c r="B20" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
+      <c r="A21" s="28"/>
       <c r="B21" s="20" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
+      <c r="A22" s="28"/>
       <c r="B22" s="20" t="s">
         <v>48</v>
       </c>
@@ -1665,106 +1665,106 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="24">
         <v>19</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="25"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="25">
+      <c r="A3" s="26"/>
+      <c r="B3" s="24">
         <v>20</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="25"/>
+      <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="25">
+      <c r="A4" s="26"/>
+      <c r="B4" s="24">
         <v>21</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="25"/>
+      <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="27"/>
-      <c r="B5" s="25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="24">
         <v>22</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="25"/>
+      <c r="D5" s="24"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
-      <c r="B6" s="25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="24">
         <v>23</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="25"/>
+      <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="25">
+      <c r="A7" s="26"/>
+      <c r="B7" s="24">
         <v>26</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="25">
+      <c r="A8" s="26"/>
+      <c r="B8" s="24">
         <v>27</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="25"/>
+      <c r="D8" s="24"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="24">
         <v>28</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="25"/>
+      <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="24">
         <v>29</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="25"/>
+      <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="25">
+      <c r="A11" s="27"/>
+      <c r="B11" s="24">
         <v>30</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="25"/>
+      <c r="D11" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/doc/计划.xlsx
+++ b/doc/计划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\code\Ey\stocking\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EA2221-8D76-4D91-B468-F1F56E7B1E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749B3B4C-B11E-4672-8BF5-9C993129B9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
   <si>
     <t>pandas</t>
   </si>
@@ -638,6 +638,13 @@
   </si>
   <si>
     <t>deepagent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.runoob.com/ai-agent/deep-agents-usage.html</t>
+  </si>
+  <si>
+    <t>tools</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1395,43 +1402,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E5E738-379F-4E22-A7E8-20617228824E}">
-  <dimension ref="B1:B7"/>
+  <dimension ref="B1:D7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>82</v>
       </c>
@@ -1777,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB402D8-2BD3-48B0-AFD0-4CCBBB667814}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
@@ -1811,6 +1821,11 @@
         <v>74</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/计划.xlsx
+++ b/doc/计划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\code\Ey\stocking\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749B3B4C-B11E-4672-8BF5-9C993129B9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E546684-17EC-4667-A365-668230ED15F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
   <si>
     <t>pandas</t>
   </si>
@@ -641,10 +641,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>tools</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.runoob.com/ai-agent/deep-agents-usage.html</t>
-  </si>
-  <si>
-    <t>tools</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[query_kline_day, query_kline_week, query_index_day, query_index_week,get_index_membership ]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -879,7 +888,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -947,6 +956,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -956,9 +968,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1282,7 +1293,7 @@
       <c r="B5" s="15"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="25" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -1290,23 +1301,23 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="25" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -1314,25 +1325,25 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="21" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="25" t="s">
         <v>41</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -1340,11 +1351,11 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
+      <c r="A15" s="25"/>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="25" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="20" t="s">
@@ -1352,11 +1363,11 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="20"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="20" t="s">
@@ -1364,25 +1375,25 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
+      <c r="A19" s="25"/>
       <c r="B19" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
+      <c r="A20" s="25"/>
       <c r="B20" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="20" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
+      <c r="A22" s="25"/>
       <c r="B22" s="20" t="s">
         <v>48</v>
       </c>
@@ -1432,8 +1443,8 @@
       <c r="B5" t="s">
         <v>80</v>
       </c>
-      <c r="D5" t="s">
-        <v>83</v>
+      <c r="D5" s="29" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
@@ -1448,6 +1459,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{826CA074-A58D-418C-9133-0F2289A77709}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1675,7 +1689,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="24">
@@ -1687,7 +1701,7 @@
       <c r="D2" s="24"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="24">
         <v>20</v>
       </c>
@@ -1697,7 +1711,7 @@
       <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="24">
         <v>21</v>
       </c>
@@ -1707,7 +1721,7 @@
       <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="24">
         <v>22</v>
       </c>
@@ -1717,7 +1731,7 @@
       <c r="D5" s="24"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="24">
         <v>23</v>
       </c>
@@ -1727,7 +1741,7 @@
       <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="24">
         <v>26</v>
       </c>
@@ -1737,7 +1751,7 @@
       <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="24">
         <v>27</v>
       </c>
@@ -1747,7 +1761,7 @@
       <c r="D8" s="24"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="24">
         <v>28</v>
       </c>
@@ -1757,7 +1771,7 @@
       <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="24">
         <v>29</v>
       </c>
@@ -1767,7 +1781,7 @@
       <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="24">
         <v>30</v>
       </c>
@@ -1787,7 +1801,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB402D8-2BD3-48B0-AFD0-4CCBBB667814}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
@@ -1823,11 +1837,20 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/计划.xlsx
+++ b/doc/计划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\code\Ey\stocking\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E546684-17EC-4667-A365-668230ED15F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3814235-F324-4E72-AECC-8B6E008DA263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="98">
   <si>
     <t>pandas</t>
   </si>
@@ -605,10 +605,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>技术关联性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -641,10 +637,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>tools</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.runoob.com/ai-agent/deep-agents-usage.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -654,6 +646,57 @@
   </si>
   <si>
     <t>[query_kline_day, query_kline_week, query_index_day, query_index_week,get_index_membership ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>权限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展示可用的主题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主题列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>agent tools</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提供的tools函数， 通过看板内的stock code, 主题描述, 由agent自行选取kline, 指数data等数据,以及可能存在的扩展性数据获取, 最后得出结论, 选取的结果是否合适, 评价类数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.runoob.com/ai-agent/deep-agents-usage.html</t>
+  </si>
+  <si>
+    <t>爬取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股吧数据, 解析成向量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按时间分组, 供agent 使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ai解析功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -956,6 +999,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -968,8 +1013,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1293,7 +1336,7 @@
       <c r="B5" s="15"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="27" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -1301,23 +1344,23 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="20"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -1325,25 +1368,25 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="19" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="21" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="27" t="s">
         <v>41</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -1351,11 +1394,11 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="20"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="27" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="20" t="s">
@@ -1363,11 +1406,11 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="20"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="27" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="20" t="s">
@@ -1375,25 +1418,25 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="20" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="20" t="s">
         <v>48</v>
       </c>
@@ -1417,44 +1460,48 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="74.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>84</v>
+        <v>79</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1685,11 +1732,11 @@
         <v>59</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>58</v>
       </c>
       <c r="B2" s="24">
@@ -1701,7 +1748,7 @@
       <c r="D2" s="24"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="24">
         <v>20</v>
       </c>
@@ -1711,7 +1758,7 @@
       <c r="D3" s="24"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
+      <c r="A4" s="29"/>
       <c r="B4" s="24">
         <v>21</v>
       </c>
@@ -1721,7 +1768,7 @@
       <c r="D4" s="24"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="27"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="24">
         <v>22</v>
       </c>
@@ -1731,7 +1778,7 @@
       <c r="D5" s="24"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="24">
         <v>23</v>
       </c>
@@ -1741,7 +1788,7 @@
       <c r="D6" s="24"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="24">
         <v>26</v>
       </c>
@@ -1751,7 +1798,7 @@
       <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="24">
         <v>27</v>
       </c>
@@ -1761,7 +1808,7 @@
       <c r="D8" s="24"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="24">
         <v>28</v>
       </c>
@@ -1771,7 +1818,7 @@
       <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="24">
         <v>29</v>
       </c>
@@ -1781,7 +1828,7 @@
       <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="24">
         <v>30</v>
       </c>
@@ -1801,7 +1848,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB402D8-2BD3-48B0-AFD0-4CCBBB667814}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
@@ -1820,32 +1867,68 @@
         <v>69</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>83</v>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>86</v>
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
